--- a/Kim-et-al-Private-Equity-Deal-List-with-Exit.xlsx
+++ b/Kim-et-al-Private-Equity-Deal-List-with-Exit.xlsx
@@ -3348,6 +3348,9 @@
     <t>D-039</t>
   </si>
   <si>
+    <t>D-096</t>
+  </si>
+  <si>
     <t>D-022</t>
   </si>
   <si>
@@ -3396,9 +3399,6 @@
     <t>D-118</t>
   </si>
   <si>
-    <t>D-096</t>
-  </si>
-  <si>
     <t>D-098</t>
   </si>
   <si>
@@ -4737,10 +4737,10 @@
     <t>St. Joseph Healthcare System</t>
   </si>
   <si>
+    <t>Albuquerque Regional Med Ctr</t>
+  </si>
+  <si>
     <t>Lovelace Health Systems</t>
-  </si>
-  <si>
-    <t>Albuquerque Regional Med Ctr</t>
   </si>
   <si>
     <t>Lovelace Medical Center</t>
@@ -9832,7 +9832,7 @@
         <v>558</v>
       </c>
       <c r="C3" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D3" s="1">
         <v>2015</v>
@@ -9897,7 +9897,7 @@
         <v>558</v>
       </c>
       <c r="C4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D4" s="1">
         <v>2018</v>
@@ -9962,7 +9962,7 @@
         <v>558</v>
       </c>
       <c r="C5" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D5" s="1">
         <v>2021</v>
@@ -10023,7 +10023,7 @@
         <v>559</v>
       </c>
       <c r="C6" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D6" s="1">
         <v>2008</v>
@@ -10088,7 +10088,7 @@
         <v>560</v>
       </c>
       <c r="C7" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D7" s="1">
         <v>2017</v>
@@ -10149,7 +10149,7 @@
         <v>561</v>
       </c>
       <c r="C8" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D8" s="1">
         <v>2018</v>
@@ -10214,7 +10214,7 @@
         <v>561</v>
       </c>
       <c r="C9" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D9" s="1">
         <v>2021</v>
@@ -10275,7 +10275,7 @@
         <v>562</v>
       </c>
       <c r="C10" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D10" s="1">
         <v>2018</v>
@@ -10336,7 +10336,7 @@
         <v>563</v>
       </c>
       <c r="C11" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D11" s="1">
         <v>2018</v>
@@ -10397,7 +10397,7 @@
         <v>564</v>
       </c>
       <c r="C12" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D12" s="1">
         <v>2008</v>
@@ -10462,7 +10462,7 @@
         <v>565</v>
       </c>
       <c r="C13" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D13" s="1">
         <v>2018</v>
@@ -10523,7 +10523,7 @@
         <v>566</v>
       </c>
       <c r="C14" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D14" s="1">
         <v>2004</v>
@@ -10586,7 +10586,7 @@
         <v>566</v>
       </c>
       <c r="C15" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D15" s="1">
         <v>2010</v>
@@ -10649,7 +10649,7 @@
         <v>567</v>
       </c>
       <c r="C16" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D16" s="1">
         <v>2005</v>
@@ -10712,7 +10712,7 @@
         <v>568</v>
       </c>
       <c r="C17" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D17" s="1">
         <v>2018</v>
@@ -10773,7 +10773,7 @@
         <v>569</v>
       </c>
       <c r="C18" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D18" s="1">
         <v>2008</v>
@@ -10834,7 +10834,7 @@
         <v>570</v>
       </c>
       <c r="C19" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D19" s="1">
         <v>2018</v>
@@ -10895,7 +10895,7 @@
         <v>571</v>
       </c>
       <c r="C20" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D20" s="1">
         <v>2018</v>
@@ -10960,7 +10960,7 @@
         <v>571</v>
       </c>
       <c r="C21" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D21" s="1">
         <v>2021</v>
@@ -11021,7 +11021,7 @@
         <v>572</v>
       </c>
       <c r="C22" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D22" s="1">
         <v>2005</v>
@@ -11084,7 +11084,7 @@
         <v>573</v>
       </c>
       <c r="C23" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D23" s="1">
         <v>2018</v>
@@ -11145,7 +11145,7 @@
         <v>574</v>
       </c>
       <c r="C24" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D24" s="1">
         <v>2008</v>
@@ -11210,7 +11210,7 @@
         <v>575</v>
       </c>
       <c r="C25" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D25" s="1">
         <v>2008</v>
@@ -11275,7 +11275,7 @@
         <v>576</v>
       </c>
       <c r="C26" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D26" s="1">
         <v>2017</v>
@@ -11399,7 +11399,7 @@
         <v>577</v>
       </c>
       <c r="C28" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D28" s="1">
         <v>2015</v>
@@ -11464,7 +11464,7 @@
         <v>577</v>
       </c>
       <c r="C29" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D29" s="1">
         <v>2018</v>
@@ -11529,7 +11529,7 @@
         <v>577</v>
       </c>
       <c r="C30" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D30" s="1">
         <v>2021</v>
@@ -11590,7 +11590,7 @@
         <v>578</v>
       </c>
       <c r="C31" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D31" s="1">
         <v>2018</v>
@@ -11651,7 +11651,7 @@
         <v>579</v>
       </c>
       <c r="C32" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D32" s="1">
         <v>2006</v>
@@ -11716,7 +11716,7 @@
         <v>580</v>
       </c>
       <c r="C33" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D33" s="1">
         <v>2004</v>
@@ -11781,7 +11781,7 @@
         <v>581</v>
       </c>
       <c r="C34" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D34" s="1">
         <v>2004</v>
@@ -11846,7 +11846,7 @@
         <v>582</v>
       </c>
       <c r="C35" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D35" s="1">
         <v>2001</v>
@@ -11909,7 +11909,7 @@
         <v>582</v>
       </c>
       <c r="C36" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D36" s="1">
         <v>2004</v>
@@ -11974,7 +11974,7 @@
         <v>583</v>
       </c>
       <c r="C37" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D37" s="1">
         <v>2001</v>
@@ -12039,7 +12039,7 @@
         <v>583</v>
       </c>
       <c r="C38" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D38" s="1">
         <v>2004</v>
@@ -12104,7 +12104,7 @@
         <v>583</v>
       </c>
       <c r="C39" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D39" s="1">
         <v>2017</v>
@@ -12169,7 +12169,7 @@
         <v>583</v>
       </c>
       <c r="C40" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D40" s="1">
         <v>2001</v>
@@ -12234,7 +12234,7 @@
         <v>583</v>
       </c>
       <c r="C41" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D41" s="1">
         <v>2004</v>
@@ -12299,7 +12299,7 @@
         <v>584</v>
       </c>
       <c r="C42" t="s">
-        <v>1127</v>
+        <v>1111</v>
       </c>
       <c r="D42" s="1">
         <v>2015</v>
@@ -12364,7 +12364,7 @@
         <v>584</v>
       </c>
       <c r="C43" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D43" s="1">
         <v>2018</v>
@@ -12429,7 +12429,7 @@
         <v>584</v>
       </c>
       <c r="C44" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D44" s="1">
         <v>2021</v>
@@ -12490,7 +12490,7 @@
         <v>585</v>
       </c>
       <c r="C45" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D45" s="1">
         <v>2018</v>
@@ -12555,7 +12555,7 @@
         <v>585</v>
       </c>
       <c r="C46" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D46" s="1">
         <v>2021</v>
@@ -12679,7 +12679,7 @@
         <v>586</v>
       </c>
       <c r="C48" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D48" s="1">
         <v>2004</v>
@@ -12744,7 +12744,7 @@
         <v>587</v>
       </c>
       <c r="C49" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D49" s="1">
         <v>2018</v>
@@ -12868,7 +12868,7 @@
         <v>588</v>
       </c>
       <c r="C51" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D51" s="1">
         <v>2004</v>
@@ -12933,7 +12933,7 @@
         <v>589</v>
       </c>
       <c r="C52" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D52" s="1">
         <v>2018</v>
@@ -13059,7 +13059,7 @@
         <v>591</v>
       </c>
       <c r="C54" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D54" s="1">
         <v>2004</v>
@@ -13313,7 +13313,7 @@
         <v>595</v>
       </c>
       <c r="C58" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D58" s="1">
         <v>2018</v>
@@ -13374,7 +13374,7 @@
         <v>596</v>
       </c>
       <c r="C59" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D59" s="1">
         <v>2018</v>
@@ -13439,7 +13439,7 @@
         <v>596</v>
       </c>
       <c r="C60" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D60" s="1">
         <v>2021</v>
@@ -13500,7 +13500,7 @@
         <v>597</v>
       </c>
       <c r="C61" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D61" s="1">
         <v>2017</v>
@@ -13746,7 +13746,7 @@
         <v>600</v>
       </c>
       <c r="C65" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D65" s="1">
         <v>2018</v>
@@ -13807,7 +13807,7 @@
         <v>601</v>
       </c>
       <c r="C66" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D66" s="1">
         <v>2018</v>
@@ -13868,7 +13868,7 @@
         <v>602</v>
       </c>
       <c r="C67" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D67" s="1">
         <v>2017</v>
@@ -13929,7 +13929,7 @@
         <v>603</v>
       </c>
       <c r="C68" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D68" s="1">
         <v>2018</v>
@@ -13990,7 +13990,7 @@
         <v>604</v>
       </c>
       <c r="C69" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D69" s="1">
         <v>2008</v>
@@ -14118,7 +14118,7 @@
         <v>604</v>
       </c>
       <c r="C71" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D71" s="1">
         <v>2018</v>
@@ -14183,7 +14183,7 @@
         <v>604</v>
       </c>
       <c r="C72" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D72" s="1">
         <v>2021</v>
@@ -14244,7 +14244,7 @@
         <v>605</v>
       </c>
       <c r="C73" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D73" s="1">
         <v>2018</v>
@@ -14305,7 +14305,7 @@
         <v>606</v>
       </c>
       <c r="C74" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D74" s="1">
         <v>2008</v>
@@ -14433,7 +14433,7 @@
         <v>606</v>
       </c>
       <c r="C76" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D76" s="1">
         <v>2018</v>
@@ -14498,7 +14498,7 @@
         <v>606</v>
       </c>
       <c r="C77" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D77" s="1">
         <v>2021</v>
@@ -14559,7 +14559,7 @@
         <v>607</v>
       </c>
       <c r="C78" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D78" s="1">
         <v>2021</v>
@@ -14620,7 +14620,7 @@
         <v>608</v>
       </c>
       <c r="C79" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D79" s="1">
         <v>2017</v>
@@ -14681,7 +14681,7 @@
         <v>609</v>
       </c>
       <c r="C80" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D80" s="1">
         <v>2018</v>
@@ -14868,7 +14868,7 @@
         <v>611</v>
       </c>
       <c r="C83" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D83" s="1">
         <v>2018</v>
@@ -14929,7 +14929,7 @@
         <v>612</v>
       </c>
       <c r="C84" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D84" s="1">
         <v>2017</v>
@@ -14994,7 +14994,7 @@
         <v>613</v>
       </c>
       <c r="C85" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D85" s="1">
         <v>2006</v>
@@ -15185,7 +15185,7 @@
         <v>616</v>
       </c>
       <c r="C88" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D88" s="1">
         <v>2006</v>
@@ -15443,7 +15443,7 @@
         <v>619</v>
       </c>
       <c r="C92" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D92" s="1">
         <v>2017</v>
@@ -15632,7 +15632,7 @@
         <v>622</v>
       </c>
       <c r="C95" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D95" s="1">
         <v>2017</v>
@@ -15693,7 +15693,7 @@
         <v>623</v>
       </c>
       <c r="C96" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D96" s="1">
         <v>2006</v>
@@ -15758,7 +15758,7 @@
         <v>624</v>
       </c>
       <c r="C97" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D97" s="1">
         <v>2004</v>
@@ -15884,7 +15884,7 @@
         <v>626</v>
       </c>
       <c r="C99" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D99" s="1">
         <v>2006</v>
@@ -16014,7 +16014,7 @@
         <v>628</v>
       </c>
       <c r="C101" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D101" s="1">
         <v>2004</v>
@@ -16079,7 +16079,7 @@
         <v>629</v>
       </c>
       <c r="C102" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D102" s="1">
         <v>2006</v>
@@ -16205,7 +16205,7 @@
         <v>631</v>
       </c>
       <c r="C104" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D104" s="1">
         <v>2004</v>
@@ -16528,7 +16528,7 @@
         <v>635</v>
       </c>
       <c r="C109" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D109" s="1">
         <v>2006</v>
@@ -16593,7 +16593,7 @@
         <v>636</v>
       </c>
       <c r="C110" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D110" s="1">
         <v>2006</v>
@@ -16658,7 +16658,7 @@
         <v>637</v>
       </c>
       <c r="C111" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D111" s="1">
         <v>2006</v>
@@ -16723,7 +16723,7 @@
         <v>638</v>
       </c>
       <c r="C112" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D112" s="1">
         <v>2018</v>
@@ -16788,7 +16788,7 @@
         <v>638</v>
       </c>
       <c r="C113" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D113" s="1">
         <v>2021</v>
@@ -16851,7 +16851,7 @@
         <v>639</v>
       </c>
       <c r="C114" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D114" s="1">
         <v>2006</v>
@@ -16916,7 +16916,7 @@
         <v>640</v>
       </c>
       <c r="C115" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D115" s="1">
         <v>2006</v>
@@ -16981,7 +16981,7 @@
         <v>641</v>
       </c>
       <c r="C116" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D116" s="1">
         <v>2006</v>
@@ -17176,7 +17176,7 @@
         <v>642</v>
       </c>
       <c r="C119" t="s">
-        <v>1127</v>
+        <v>1111</v>
       </c>
       <c r="D119" s="1">
         <v>2015</v>
@@ -17434,7 +17434,7 @@
         <v>646</v>
       </c>
       <c r="C123" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D123" s="1">
         <v>2006</v>
@@ -17627,7 +17627,7 @@
         <v>649</v>
       </c>
       <c r="C126" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D126" s="1">
         <v>2018</v>
@@ -17688,7 +17688,7 @@
         <v>650</v>
       </c>
       <c r="C127" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D127" s="1">
         <v>2018</v>
@@ -17812,7 +17812,7 @@
         <v>652</v>
       </c>
       <c r="C129" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D129" s="1">
         <v>2006</v>
@@ -17877,7 +17877,7 @@
         <v>653</v>
       </c>
       <c r="C130" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D130" s="1">
         <v>2018</v>
@@ -17938,7 +17938,7 @@
         <v>654</v>
       </c>
       <c r="C131" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D131" s="1">
         <v>2018</v>
@@ -17999,7 +17999,7 @@
         <v>655</v>
       </c>
       <c r="C132" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D132" s="1">
         <v>2018</v>
@@ -18060,7 +18060,7 @@
         <v>656</v>
       </c>
       <c r="C133" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D133" s="1">
         <v>2006</v>
@@ -18251,7 +18251,7 @@
         <v>658</v>
       </c>
       <c r="C136" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D136" s="1">
         <v>2018</v>
@@ -18312,7 +18312,7 @@
         <v>659</v>
       </c>
       <c r="C137" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D137" s="1">
         <v>2018</v>
@@ -18373,7 +18373,7 @@
         <v>660</v>
       </c>
       <c r="C138" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D138" s="1">
         <v>2006</v>
@@ -18438,7 +18438,7 @@
         <v>661</v>
       </c>
       <c r="C139" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D139" s="1">
         <v>2018</v>
@@ -18499,7 +18499,7 @@
         <v>662</v>
       </c>
       <c r="C140" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D140" s="1">
         <v>2018</v>
@@ -18560,7 +18560,7 @@
         <v>663</v>
       </c>
       <c r="C141" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D141" s="1">
         <v>2004</v>
@@ -18625,7 +18625,7 @@
         <v>664</v>
       </c>
       <c r="C142" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D142" s="1">
         <v>2006</v>
@@ -18690,7 +18690,7 @@
         <v>665</v>
       </c>
       <c r="C143" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D143" s="1">
         <v>2018</v>
@@ -18751,7 +18751,7 @@
         <v>666</v>
       </c>
       <c r="C144" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D144" s="1">
         <v>2018</v>
@@ -18812,7 +18812,7 @@
         <v>667</v>
       </c>
       <c r="C145" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D145" s="1">
         <v>2006</v>
@@ -18877,7 +18877,7 @@
         <v>668</v>
       </c>
       <c r="C146" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D146" s="1">
         <v>2006</v>
@@ -18942,7 +18942,7 @@
         <v>669</v>
       </c>
       <c r="C147" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D147" s="1">
         <v>2006</v>
@@ -19007,7 +19007,7 @@
         <v>670</v>
       </c>
       <c r="C148" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D148" s="1">
         <v>2006</v>
@@ -19072,7 +19072,7 @@
         <v>671</v>
       </c>
       <c r="C149" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D149" s="1">
         <v>2006</v>
@@ -19137,7 +19137,7 @@
         <v>672</v>
       </c>
       <c r="C150" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D150" s="1">
         <v>2006</v>
@@ -19328,7 +19328,7 @@
         <v>675</v>
       </c>
       <c r="C153" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D153" s="1">
         <v>2006</v>
@@ -19393,7 +19393,7 @@
         <v>676</v>
       </c>
       <c r="C154" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D154" s="1">
         <v>2006</v>
@@ -19458,7 +19458,7 @@
         <v>677</v>
       </c>
       <c r="C155" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D155" s="1">
         <v>2006</v>
@@ -19523,7 +19523,7 @@
         <v>678</v>
       </c>
       <c r="C156" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D156" s="1">
         <v>2004</v>
@@ -19588,7 +19588,7 @@
         <v>679</v>
       </c>
       <c r="C157" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D157" s="1">
         <v>2006</v>
@@ -19712,7 +19712,7 @@
         <v>681</v>
       </c>
       <c r="C159" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D159" s="1">
         <v>2006</v>
@@ -19777,7 +19777,7 @@
         <v>682</v>
       </c>
       <c r="C160" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D160" s="1">
         <v>2006</v>
@@ -19968,7 +19968,7 @@
         <v>684</v>
       </c>
       <c r="C163" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D163" s="1">
         <v>2006</v>
@@ -20033,7 +20033,7 @@
         <v>685</v>
       </c>
       <c r="C164" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D164" s="1">
         <v>2006</v>
@@ -20098,7 +20098,7 @@
         <v>686</v>
       </c>
       <c r="C165" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D165" s="1">
         <v>2006</v>
@@ -20163,7 +20163,7 @@
         <v>687</v>
       </c>
       <c r="C166" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D166" s="1">
         <v>2006</v>
@@ -20228,7 +20228,7 @@
         <v>688</v>
       </c>
       <c r="C167" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D167" s="1">
         <v>2006</v>
@@ -20293,7 +20293,7 @@
         <v>689</v>
       </c>
       <c r="C168" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D168" s="1">
         <v>2006</v>
@@ -20358,7 +20358,7 @@
         <v>690</v>
       </c>
       <c r="C169" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D169" s="1">
         <v>2006</v>
@@ -20423,7 +20423,7 @@
         <v>691</v>
       </c>
       <c r="C170" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D170" s="1">
         <v>2006</v>
@@ -20488,7 +20488,7 @@
         <v>692</v>
       </c>
       <c r="C171" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D171" s="1">
         <v>2006</v>
@@ -20553,7 +20553,7 @@
         <v>693</v>
       </c>
       <c r="C172" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D172" s="1">
         <v>2006</v>
@@ -20618,7 +20618,7 @@
         <v>694</v>
       </c>
       <c r="C173" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D173" s="1">
         <v>2006</v>
@@ -20683,7 +20683,7 @@
         <v>695</v>
       </c>
       <c r="C174" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D174" s="1">
         <v>2006</v>
@@ -20748,7 +20748,7 @@
         <v>696</v>
       </c>
       <c r="C175" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D175" s="1">
         <v>2006</v>
@@ -20813,7 +20813,7 @@
         <v>697</v>
       </c>
       <c r="C176" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D176" s="1">
         <v>2018</v>
@@ -20874,7 +20874,7 @@
         <v>698</v>
       </c>
       <c r="C177" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D177" s="1">
         <v>2006</v>
@@ -20939,7 +20939,7 @@
         <v>699</v>
       </c>
       <c r="C178" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D178" s="1">
         <v>2006</v>
@@ -21004,7 +21004,7 @@
         <v>700</v>
       </c>
       <c r="C179" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D179" s="1">
         <v>2004</v>
@@ -21069,7 +21069,7 @@
         <v>701</v>
       </c>
       <c r="C180" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D180" s="1">
         <v>2006</v>
@@ -21134,7 +21134,7 @@
         <v>702</v>
       </c>
       <c r="C181" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D181" s="1">
         <v>2006</v>
@@ -21199,7 +21199,7 @@
         <v>703</v>
       </c>
       <c r="C182" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D182" s="1">
         <v>2006</v>
@@ -21264,7 +21264,7 @@
         <v>704</v>
       </c>
       <c r="C183" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D183" s="1">
         <v>2006</v>
@@ -21329,7 +21329,7 @@
         <v>705</v>
       </c>
       <c r="C184" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D184" s="1">
         <v>2006</v>
@@ -21394,7 +21394,7 @@
         <v>706</v>
       </c>
       <c r="C185" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D185" s="1">
         <v>2006</v>
@@ -21459,7 +21459,7 @@
         <v>707</v>
       </c>
       <c r="C186" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D186" s="1">
         <v>2018</v>
@@ -21646,7 +21646,7 @@
         <v>709</v>
       </c>
       <c r="C189" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D189" s="1">
         <v>2018</v>
@@ -21768,7 +21768,7 @@
         <v>711</v>
       </c>
       <c r="C191" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D191" s="1">
         <v>2006</v>
@@ -21833,7 +21833,7 @@
         <v>712</v>
       </c>
       <c r="C192" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D192" s="1">
         <v>2006</v>
@@ -21898,7 +21898,7 @@
         <v>713</v>
       </c>
       <c r="C193" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D193" s="1">
         <v>2017</v>
@@ -21959,7 +21959,7 @@
         <v>714</v>
       </c>
       <c r="C194" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D194" s="1">
         <v>2018</v>
@@ -22020,7 +22020,7 @@
         <v>715</v>
       </c>
       <c r="C195" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D195" s="1">
         <v>2006</v>
@@ -22085,7 +22085,7 @@
         <v>716</v>
       </c>
       <c r="C196" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D196" s="1">
         <v>2018</v>
@@ -22150,7 +22150,7 @@
         <v>716</v>
       </c>
       <c r="C197" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D197" s="1">
         <v>2021</v>
@@ -22211,7 +22211,7 @@
         <v>717</v>
       </c>
       <c r="C198" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D198" s="1">
         <v>2006</v>
@@ -22276,7 +22276,7 @@
         <v>718</v>
       </c>
       <c r="C199" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D199" s="1">
         <v>2006</v>
@@ -22341,7 +22341,7 @@
         <v>719</v>
       </c>
       <c r="C200" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D200" s="1">
         <v>2006</v>
@@ -22406,7 +22406,7 @@
         <v>720</v>
       </c>
       <c r="C201" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D201" s="1">
         <v>2006</v>
@@ -22471,7 +22471,7 @@
         <v>721</v>
       </c>
       <c r="C202" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D202" s="1">
         <v>2006</v>
@@ -22536,7 +22536,7 @@
         <v>722</v>
       </c>
       <c r="C203" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D203" s="1">
         <v>2006</v>
@@ -22601,7 +22601,7 @@
         <v>723</v>
       </c>
       <c r="C204" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D204" s="1">
         <v>2017</v>
@@ -22662,7 +22662,7 @@
         <v>724</v>
       </c>
       <c r="C205" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D205" s="1">
         <v>2006</v>
@@ -22790,7 +22790,7 @@
         <v>725</v>
       </c>
       <c r="C207" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D207" s="1">
         <v>2006</v>
@@ -22855,7 +22855,7 @@
         <v>726</v>
       </c>
       <c r="C208" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D208" s="1">
         <v>2006</v>
@@ -23044,7 +23044,7 @@
         <v>729</v>
       </c>
       <c r="C211" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D211" s="1">
         <v>2006</v>
@@ -23109,7 +23109,7 @@
         <v>730</v>
       </c>
       <c r="C212" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D212" s="1">
         <v>2006</v>
@@ -23426,7 +23426,7 @@
         <v>734</v>
       </c>
       <c r="C217" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D217" s="1">
         <v>2017</v>
@@ -23487,7 +23487,7 @@
         <v>735</v>
       </c>
       <c r="C218" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D218" s="1">
         <v>2017</v>
@@ -23676,7 +23676,7 @@
         <v>737</v>
       </c>
       <c r="C221" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D221" s="1">
         <v>2004</v>
@@ -23741,7 +23741,7 @@
         <v>738</v>
       </c>
       <c r="C222" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D222" s="1">
         <v>2004</v>
@@ -23806,7 +23806,7 @@
         <v>739</v>
       </c>
       <c r="C223" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D223" s="1">
         <v>2017</v>
@@ -23993,7 +23993,7 @@
         <v>741</v>
       </c>
       <c r="C226" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D226" s="1">
         <v>2017</v>
@@ -24054,7 +24054,7 @@
         <v>742</v>
       </c>
       <c r="C227" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D227" s="1">
         <v>2017</v>
@@ -24115,7 +24115,7 @@
         <v>743</v>
       </c>
       <c r="C228" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D228" s="1">
         <v>2017</v>
@@ -24300,7 +24300,7 @@
         <v>746</v>
       </c>
       <c r="C231" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D231" s="1">
         <v>2017</v>
@@ -24361,7 +24361,7 @@
         <v>747</v>
       </c>
       <c r="C232" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D232" s="1">
         <v>2018</v>
@@ -24422,7 +24422,7 @@
         <v>748</v>
       </c>
       <c r="C233" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D233" s="1">
         <v>2018</v>
@@ -24487,7 +24487,7 @@
         <v>748</v>
       </c>
       <c r="C234" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D234" s="1">
         <v>2021</v>
@@ -24550,7 +24550,7 @@
         <v>749</v>
       </c>
       <c r="C235" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D235" s="1">
         <v>2018</v>
@@ -24611,7 +24611,7 @@
         <v>750</v>
       </c>
       <c r="C236" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D236" s="1">
         <v>2018</v>
@@ -24672,7 +24672,7 @@
         <v>751</v>
       </c>
       <c r="C237" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D237" s="1">
         <v>2006</v>
@@ -24737,7 +24737,7 @@
         <v>752</v>
       </c>
       <c r="C238" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D238" s="1">
         <v>2018</v>
@@ -24798,7 +24798,7 @@
         <v>753</v>
       </c>
       <c r="C239" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D239" s="1">
         <v>2018</v>
@@ -24859,7 +24859,7 @@
         <v>754</v>
       </c>
       <c r="C240" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D240" s="1">
         <v>2018</v>
@@ -24920,7 +24920,7 @@
         <v>755</v>
       </c>
       <c r="C241" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D241" s="1">
         <v>2018</v>
@@ -24981,7 +24981,7 @@
         <v>756</v>
       </c>
       <c r="C242" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D242" s="1">
         <v>2018</v>
@@ -25042,7 +25042,7 @@
         <v>757</v>
       </c>
       <c r="C243" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D243" s="1">
         <v>2018</v>
@@ -25168,7 +25168,7 @@
         <v>758</v>
       </c>
       <c r="C245" t="s">
-        <v>1127</v>
+        <v>1111</v>
       </c>
       <c r="D245" s="1">
         <v>2015</v>
@@ -25233,7 +25233,7 @@
         <v>758</v>
       </c>
       <c r="C246" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D246" s="1">
         <v>2018</v>
@@ -25298,7 +25298,7 @@
         <v>758</v>
       </c>
       <c r="C247" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D247" s="1">
         <v>2021</v>
@@ -25420,7 +25420,7 @@
         <v>760</v>
       </c>
       <c r="C249" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D249" s="1">
         <v>2006</v>
@@ -25485,7 +25485,7 @@
         <v>761</v>
       </c>
       <c r="C250" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D250" s="1">
         <v>2018</v>
@@ -25550,7 +25550,7 @@
         <v>761</v>
       </c>
       <c r="C251" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D251" s="1">
         <v>2021</v>
@@ -25613,7 +25613,7 @@
         <v>762</v>
       </c>
       <c r="C252" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D252" s="1">
         <v>2006</v>
@@ -25678,7 +25678,7 @@
         <v>763</v>
       </c>
       <c r="C253" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D253" s="1">
         <v>2006</v>
@@ -25926,7 +25926,7 @@
         <v>766</v>
       </c>
       <c r="C257" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D257" s="1">
         <v>2018</v>
@@ -25991,7 +25991,7 @@
         <v>766</v>
       </c>
       <c r="C258" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D258" s="1">
         <v>2021</v>
@@ -26052,7 +26052,7 @@
         <v>767</v>
       </c>
       <c r="C259" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D259" s="1">
         <v>2018</v>
@@ -26117,7 +26117,7 @@
         <v>767</v>
       </c>
       <c r="C260" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D260" s="1">
         <v>2021</v>
@@ -26178,7 +26178,7 @@
         <v>768</v>
       </c>
       <c r="C261" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D261" s="1">
         <v>2018</v>
@@ -26243,7 +26243,7 @@
         <v>768</v>
       </c>
       <c r="C262" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D262" s="1">
         <v>2021</v>
@@ -26304,7 +26304,7 @@
         <v>769</v>
       </c>
       <c r="C263" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D263" s="1">
         <v>2018</v>
@@ -26367,7 +26367,7 @@
         <v>770</v>
       </c>
       <c r="C264" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D264" s="1">
         <v>2018</v>
@@ -26432,7 +26432,7 @@
         <v>770</v>
       </c>
       <c r="C265" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D265" s="1">
         <v>2021</v>
@@ -26495,7 +26495,7 @@
         <v>771</v>
       </c>
       <c r="C266" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D266" s="1">
         <v>2017</v>
@@ -26556,7 +26556,7 @@
         <v>772</v>
       </c>
       <c r="C267" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D267" s="1">
         <v>2018</v>
@@ -26621,7 +26621,7 @@
         <v>772</v>
       </c>
       <c r="C268" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D268" s="1">
         <v>2021</v>
@@ -26682,7 +26682,7 @@
         <v>773</v>
       </c>
       <c r="C269" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D269" s="1">
         <v>2018</v>
@@ -26747,7 +26747,7 @@
         <v>773</v>
       </c>
       <c r="C270" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D270" s="1">
         <v>2021</v>
@@ -26808,7 +26808,7 @@
         <v>774</v>
       </c>
       <c r="C271" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D271" s="1">
         <v>2018</v>
@@ -26873,7 +26873,7 @@
         <v>774</v>
       </c>
       <c r="C272" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D272" s="1">
         <v>2021</v>
@@ -26934,7 +26934,7 @@
         <v>775</v>
       </c>
       <c r="C273" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D273" s="1">
         <v>2006</v>
@@ -26999,7 +26999,7 @@
         <v>776</v>
       </c>
       <c r="C274" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D274" s="1">
         <v>2006</v>
@@ -27064,7 +27064,7 @@
         <v>777</v>
       </c>
       <c r="C275" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D275" s="1">
         <v>2017</v>
@@ -27125,7 +27125,7 @@
         <v>778</v>
       </c>
       <c r="C276" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D276" s="1">
         <v>2018</v>
@@ -27190,7 +27190,7 @@
         <v>778</v>
       </c>
       <c r="C277" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D277" s="1">
         <v>2021</v>
@@ -27251,7 +27251,7 @@
         <v>779</v>
       </c>
       <c r="C278" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D278" s="1">
         <v>2017</v>
@@ -27312,7 +27312,7 @@
         <v>780</v>
       </c>
       <c r="C279" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D279" s="1">
         <v>2006</v>
@@ -27377,7 +27377,7 @@
         <v>781</v>
       </c>
       <c r="C280" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D280" s="1">
         <v>2018</v>
@@ -27442,7 +27442,7 @@
         <v>782</v>
       </c>
       <c r="C281" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D281" s="1">
         <v>2006</v>
@@ -27507,7 +27507,7 @@
         <v>783</v>
       </c>
       <c r="C282" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D282" s="1">
         <v>2006</v>
@@ -27572,7 +27572,7 @@
         <v>784</v>
       </c>
       <c r="C283" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D283" s="1">
         <v>2018</v>
@@ -27633,7 +27633,7 @@
         <v>785</v>
       </c>
       <c r="C284" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D284" s="1">
         <v>2006</v>
@@ -27698,7 +27698,7 @@
         <v>786</v>
       </c>
       <c r="C285" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D285" s="1">
         <v>2006</v>
@@ -27763,7 +27763,7 @@
         <v>787</v>
       </c>
       <c r="C286" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D286" s="1">
         <v>2006</v>
@@ -27893,7 +27893,7 @@
         <v>788</v>
       </c>
       <c r="C288" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D288" s="1">
         <v>2017</v>
@@ -27958,7 +27958,7 @@
         <v>789</v>
       </c>
       <c r="C289" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D289" s="1">
         <v>2006</v>
@@ -28023,7 +28023,7 @@
         <v>790</v>
       </c>
       <c r="C290" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D290" s="1">
         <v>2006</v>
@@ -28088,7 +28088,7 @@
         <v>791</v>
       </c>
       <c r="C291" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D291" s="1">
         <v>2006</v>
@@ -28401,7 +28401,7 @@
         <v>794</v>
       </c>
       <c r="C296" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D296" s="1">
         <v>2006</v>
@@ -30783,7 +30783,7 @@
         <v>815</v>
       </c>
       <c r="C334" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D334" s="1">
         <v>2018</v>
@@ -30848,7 +30848,7 @@
         <v>815</v>
       </c>
       <c r="C335" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D335" s="1">
         <v>2021</v>
@@ -31102,7 +31102,7 @@
         <v>819</v>
       </c>
       <c r="C339" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D339" s="1">
         <v>2018</v>
@@ -31163,7 +31163,7 @@
         <v>820</v>
       </c>
       <c r="C340" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D340" s="1">
         <v>2018</v>
@@ -31224,7 +31224,7 @@
         <v>821</v>
       </c>
       <c r="C341" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D341" s="1">
         <v>2018</v>
@@ -31285,7 +31285,7 @@
         <v>822</v>
       </c>
       <c r="C342" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D342" s="1">
         <v>2018</v>
@@ -31346,7 +31346,7 @@
         <v>823</v>
       </c>
       <c r="C343" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D343" s="1">
         <v>2018</v>
@@ -31407,7 +31407,7 @@
         <v>824</v>
       </c>
       <c r="C344" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D344" s="1">
         <v>2018</v>
@@ -31472,7 +31472,7 @@
         <v>824</v>
       </c>
       <c r="C345" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D345" s="1">
         <v>2021</v>
@@ -31533,7 +31533,7 @@
         <v>825</v>
       </c>
       <c r="C346" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D346" s="1">
         <v>2018</v>
@@ -31594,7 +31594,7 @@
         <v>826</v>
       </c>
       <c r="C347" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D347" s="1">
         <v>2018</v>
@@ -31655,7 +31655,7 @@
         <v>827</v>
       </c>
       <c r="C348" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D348" s="1">
         <v>2006</v>
@@ -31720,7 +31720,7 @@
         <v>828</v>
       </c>
       <c r="C349" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D349" s="1">
         <v>2018</v>
@@ -31781,7 +31781,7 @@
         <v>829</v>
       </c>
       <c r="C350" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D350" s="1">
         <v>2018</v>
@@ -31842,7 +31842,7 @@
         <v>830</v>
       </c>
       <c r="C351" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D351" s="1">
         <v>2018</v>
@@ -31903,7 +31903,7 @@
         <v>831</v>
       </c>
       <c r="C352" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D352" s="1">
         <v>2018</v>
@@ -31964,7 +31964,7 @@
         <v>832</v>
       </c>
       <c r="C353" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D353" s="1">
         <v>2006</v>
@@ -32029,7 +32029,7 @@
         <v>833</v>
       </c>
       <c r="C354" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D354" s="1">
         <v>2018</v>
@@ -32090,7 +32090,7 @@
         <v>834</v>
       </c>
       <c r="C355" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D355" s="1">
         <v>2006</v>
@@ -32220,7 +32220,7 @@
         <v>836</v>
       </c>
       <c r="C357" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D357" s="1">
         <v>2018</v>
@@ -32281,7 +32281,7 @@
         <v>837</v>
       </c>
       <c r="C358" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D358" s="1">
         <v>2006</v>
@@ -32346,7 +32346,7 @@
         <v>838</v>
       </c>
       <c r="C359" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D359" s="1">
         <v>2006</v>
@@ -32598,7 +32598,7 @@
         <v>841</v>
       </c>
       <c r="C363" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D363" s="1">
         <v>2006</v>
@@ -32663,7 +32663,7 @@
         <v>842</v>
       </c>
       <c r="C364" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D364" s="1">
         <v>2018</v>
@@ -32728,7 +32728,7 @@
         <v>842</v>
       </c>
       <c r="C365" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D365" s="1">
         <v>2021</v>
@@ -32850,7 +32850,7 @@
         <v>844</v>
       </c>
       <c r="C367" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D367" s="1">
         <v>2006</v>
@@ -32978,7 +32978,7 @@
         <v>845</v>
       </c>
       <c r="C369" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D369" s="1">
         <v>2004</v>
@@ -33043,7 +33043,7 @@
         <v>846</v>
       </c>
       <c r="C370" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D370" s="1">
         <v>2018</v>
@@ -33108,7 +33108,7 @@
         <v>846</v>
       </c>
       <c r="C371" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D371" s="1">
         <v>2021</v>
@@ -33169,7 +33169,7 @@
         <v>847</v>
       </c>
       <c r="C372" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D372" s="1">
         <v>2006</v>
@@ -33234,7 +33234,7 @@
         <v>848</v>
       </c>
       <c r="C373" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D373" s="1">
         <v>2006</v>
@@ -33299,7 +33299,7 @@
         <v>849</v>
       </c>
       <c r="C374" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D374" s="1">
         <v>2006</v>
@@ -33364,7 +33364,7 @@
         <v>850</v>
       </c>
       <c r="C375" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D375" s="1">
         <v>2006</v>
@@ -33744,7 +33744,7 @@
         <v>853</v>
       </c>
       <c r="C381" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D381" s="1">
         <v>2018</v>
@@ -33931,7 +33931,7 @@
         <v>855</v>
       </c>
       <c r="C384" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D384" s="1">
         <v>2017</v>
@@ -33992,7 +33992,7 @@
         <v>856</v>
       </c>
       <c r="C385" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D385" s="1">
         <v>2018</v>
@@ -34118,7 +34118,7 @@
         <v>857</v>
       </c>
       <c r="C387" t="s">
-        <v>1205</v>
+        <v>1175</v>
       </c>
       <c r="D387" s="1">
         <v>2003</v>
@@ -34139,32 +34139,28 @@
         <v>87102</v>
       </c>
       <c r="J387" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K387" t="s">
-        <v>2899</v>
+        <v>2917</v>
       </c>
       <c r="L387" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="M387" s="2"/>
-      <c r="N387" s="2">
-        <v>37636</v>
-      </c>
+      <c r="N387" s="2"/>
       <c r="O387" t="s">
         <v>2899</v>
       </c>
       <c r="P387" t="s">
-        <v>3058</v>
+        <v>2899</v>
       </c>
       <c r="Q387" t="s">
-        <v>3088</v>
-      </c>
-      <c r="R387" s="2">
-        <v>42192</v>
-      </c>
+        <v>2899</v>
+      </c>
+      <c r="R387" s="2"/>
       <c r="S387" t="s">
-        <v>3059</v>
+        <v>2899</v>
       </c>
       <c r="T387" s="1">
         <v>0</v>
@@ -34181,7 +34177,7 @@
         <v>857</v>
       </c>
       <c r="C388" t="s">
-        <v>1175</v>
+        <v>1205</v>
       </c>
       <c r="D388" s="1">
         <v>2003</v>
@@ -34202,28 +34198,32 @@
         <v>87102</v>
       </c>
       <c r="J388" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K388" t="s">
-        <v>2917</v>
+        <v>2899</v>
       </c>
       <c r="L388" t="s">
-        <v>2932</v>
+        <v>2930</v>
       </c>
       <c r="M388" s="2"/>
-      <c r="N388" s="2"/>
+      <c r="N388" s="2">
+        <v>37636</v>
+      </c>
       <c r="O388" t="s">
         <v>2899</v>
       </c>
       <c r="P388" t="s">
-        <v>2899</v>
+        <v>3058</v>
       </c>
       <c r="Q388" t="s">
-        <v>2899</v>
-      </c>
-      <c r="R388" s="2"/>
+        <v>3088</v>
+      </c>
+      <c r="R388" s="2">
+        <v>42192</v>
+      </c>
       <c r="S388" t="s">
-        <v>2899</v>
+        <v>3059</v>
       </c>
       <c r="T388" s="1">
         <v>0</v>
@@ -34368,7 +34368,7 @@
         <v>2003</v>
       </c>
       <c r="E391" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="F391" t="s">
         <v>2089</v>
@@ -34488,7 +34488,7 @@
         <v>859</v>
       </c>
       <c r="C393" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D393" s="1">
         <v>2018</v>
@@ -34553,7 +34553,7 @@
         <v>859</v>
       </c>
       <c r="C394" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D394" s="1">
         <v>2021</v>
@@ -34620,7 +34620,7 @@
         <v>2003</v>
       </c>
       <c r="E395" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="F395" t="s">
         <v>2089</v>
@@ -34677,7 +34677,7 @@
         <v>861</v>
       </c>
       <c r="C396" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D396" s="1">
         <v>2018</v>
@@ -34742,7 +34742,7 @@
         <v>861</v>
       </c>
       <c r="C397" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D397" s="1">
         <v>2021</v>
@@ -34803,7 +34803,7 @@
         <v>862</v>
       </c>
       <c r="C398" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D398" s="1">
         <v>2018</v>
@@ -34864,7 +34864,7 @@
         <v>863</v>
       </c>
       <c r="C399" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D399" s="1">
         <v>2018</v>
@@ -34925,13 +34925,13 @@
         <v>864</v>
       </c>
       <c r="C400" t="s">
-        <v>1205</v>
+        <v>1175</v>
       </c>
       <c r="D400" s="1">
         <v>2003</v>
       </c>
       <c r="E400" t="s">
-        <v>1574</v>
+        <v>1583</v>
       </c>
       <c r="F400" t="s">
         <v>2089</v>
@@ -34946,32 +34946,28 @@
         <v>87114</v>
       </c>
       <c r="J400" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K400" t="s">
-        <v>2899</v>
+        <v>2917</v>
       </c>
       <c r="L400" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="M400" s="2"/>
-      <c r="N400" s="2">
-        <v>37636</v>
-      </c>
+      <c r="N400" s="2"/>
       <c r="O400" t="s">
         <v>2899</v>
       </c>
       <c r="P400" t="s">
-        <v>3058</v>
+        <v>2899</v>
       </c>
       <c r="Q400" t="s">
-        <v>3088</v>
-      </c>
-      <c r="R400" s="2">
-        <v>42192</v>
-      </c>
+        <v>2899</v>
+      </c>
+      <c r="R400" s="2"/>
       <c r="S400" t="s">
-        <v>3059</v>
+        <v>2899</v>
       </c>
       <c r="T400" s="1">
         <v>0</v>
@@ -34988,13 +34984,13 @@
         <v>864</v>
       </c>
       <c r="C401" t="s">
-        <v>1175</v>
+        <v>1205</v>
       </c>
       <c r="D401" s="1">
         <v>2003</v>
       </c>
       <c r="E401" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="F401" t="s">
         <v>2089</v>
@@ -35009,28 +35005,32 @@
         <v>87114</v>
       </c>
       <c r="J401" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K401" t="s">
-        <v>2917</v>
+        <v>2899</v>
       </c>
       <c r="L401" t="s">
-        <v>2932</v>
+        <v>2930</v>
       </c>
       <c r="M401" s="2"/>
-      <c r="N401" s="2"/>
+      <c r="N401" s="2">
+        <v>37636</v>
+      </c>
       <c r="O401" t="s">
         <v>2899</v>
       </c>
       <c r="P401" t="s">
-        <v>2899</v>
+        <v>3058</v>
       </c>
       <c r="Q401" t="s">
-        <v>2899</v>
-      </c>
-      <c r="R401" s="2"/>
+        <v>3088</v>
+      </c>
+      <c r="R401" s="2">
+        <v>42192</v>
+      </c>
       <c r="S401" t="s">
-        <v>2899</v>
+        <v>3059</v>
       </c>
       <c r="T401" s="1">
         <v>0</v>
@@ -35110,7 +35110,7 @@
         <v>865</v>
       </c>
       <c r="C403" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D403" s="1">
         <v>2018</v>
@@ -35360,7 +35360,7 @@
         <v>868</v>
       </c>
       <c r="C407" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D407" s="1">
         <v>2018</v>
@@ -35421,7 +35421,7 @@
         <v>869</v>
       </c>
       <c r="C408" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D408" s="1">
         <v>2017</v>
@@ -35482,7 +35482,7 @@
         <v>870</v>
       </c>
       <c r="C409" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D409" s="1">
         <v>2018</v>
@@ -35795,7 +35795,7 @@
         <v>873</v>
       </c>
       <c r="C414" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D414" s="1">
         <v>2017</v>
@@ -35856,7 +35856,7 @@
         <v>874</v>
       </c>
       <c r="C415" t="s">
-        <v>1127</v>
+        <v>1111</v>
       </c>
       <c r="D415" s="1">
         <v>2015</v>
@@ -35921,7 +35921,7 @@
         <v>874</v>
       </c>
       <c r="C416" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D416" s="1">
         <v>2018</v>
@@ -35986,7 +35986,7 @@
         <v>874</v>
       </c>
       <c r="C417" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D417" s="1">
         <v>2021</v>
@@ -36177,7 +36177,7 @@
         <v>876</v>
       </c>
       <c r="C420" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D420" s="1">
         <v>2018</v>
@@ -36238,7 +36238,7 @@
         <v>877</v>
       </c>
       <c r="C421" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D421" s="1">
         <v>2018</v>
@@ -36299,7 +36299,7 @@
         <v>878</v>
       </c>
       <c r="C422" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D422" s="1">
         <v>2018</v>
@@ -36486,7 +36486,7 @@
         <v>880</v>
       </c>
       <c r="C425" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D425" s="1">
         <v>2018</v>
@@ -36547,7 +36547,7 @@
         <v>881</v>
       </c>
       <c r="C426" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D426" s="1">
         <v>2018</v>
@@ -36736,7 +36736,7 @@
         <v>884</v>
       </c>
       <c r="C429" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D429" s="1">
         <v>2006</v>
@@ -36801,7 +36801,7 @@
         <v>885</v>
       </c>
       <c r="C430" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D430" s="1">
         <v>2018</v>
@@ -36990,7 +36990,7 @@
         <v>886</v>
       </c>
       <c r="C433" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D433" s="1">
         <v>2018</v>
@@ -37055,7 +37055,7 @@
         <v>886</v>
       </c>
       <c r="C434" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D434" s="1">
         <v>2021</v>
@@ -37246,7 +37246,7 @@
         <v>888</v>
       </c>
       <c r="C437" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D437" s="1">
         <v>2006</v>
@@ -37758,7 +37758,7 @@
         <v>894</v>
       </c>
       <c r="C445" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D445" s="1">
         <v>2018</v>
@@ -37882,7 +37882,7 @@
         <v>896</v>
       </c>
       <c r="C447" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D447" s="1">
         <v>2017</v>
@@ -37943,7 +37943,7 @@
         <v>897</v>
       </c>
       <c r="C448" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D448" s="1">
         <v>2008</v>
@@ -38071,7 +38071,7 @@
         <v>897</v>
       </c>
       <c r="C450" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D450" s="1">
         <v>2018</v>
@@ -38136,7 +38136,7 @@
         <v>897</v>
       </c>
       <c r="C451" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D451" s="1">
         <v>2021</v>
@@ -38197,7 +38197,7 @@
         <v>898</v>
       </c>
       <c r="C452" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D452" s="1">
         <v>2018</v>
@@ -38262,7 +38262,7 @@
         <v>898</v>
       </c>
       <c r="C453" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D453" s="1">
         <v>2021</v>
@@ -38323,7 +38323,7 @@
         <v>899</v>
       </c>
       <c r="C454" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D454" s="1">
         <v>2017</v>
@@ -38384,7 +38384,7 @@
         <v>900</v>
       </c>
       <c r="C455" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D455" s="1">
         <v>2018</v>
@@ -38508,7 +38508,7 @@
         <v>902</v>
       </c>
       <c r="C457" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D457" s="1">
         <v>2017</v>
@@ -38569,7 +38569,7 @@
         <v>903</v>
       </c>
       <c r="C458" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D458" s="1">
         <v>2018</v>
@@ -38630,7 +38630,7 @@
         <v>904</v>
       </c>
       <c r="C459" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D459" s="1">
         <v>2018</v>
@@ -39010,7 +39010,7 @@
         <v>908</v>
       </c>
       <c r="C465" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D465" s="1">
         <v>2018</v>
@@ -39197,7 +39197,7 @@
         <v>910</v>
       </c>
       <c r="C468" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D468" s="1">
         <v>2018</v>
@@ -39510,7 +39510,7 @@
         <v>913</v>
       </c>
       <c r="C473" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D473" s="1">
         <v>2018</v>
@@ -39575,7 +39575,7 @@
         <v>913</v>
       </c>
       <c r="C474" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D474" s="1">
         <v>2021</v>
@@ -39636,7 +39636,7 @@
         <v>914</v>
       </c>
       <c r="C475" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D475" s="1">
         <v>2018</v>
@@ -39697,7 +39697,7 @@
         <v>915</v>
       </c>
       <c r="C476" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D476" s="1">
         <v>2018</v>
@@ -39762,7 +39762,7 @@
         <v>916</v>
       </c>
       <c r="C477" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D477" s="1">
         <v>2006</v>
@@ -39827,7 +39827,7 @@
         <v>917</v>
       </c>
       <c r="C478" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D478" s="1">
         <v>2018</v>
@@ -39888,7 +39888,7 @@
         <v>918</v>
       </c>
       <c r="C479" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D479" s="1">
         <v>2018</v>
@@ -40073,7 +40073,7 @@
         <v>919</v>
       </c>
       <c r="C482" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D482" s="1">
         <v>2018</v>
@@ -40138,7 +40138,7 @@
         <v>920</v>
       </c>
       <c r="C483" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D483" s="1">
         <v>2018</v>
@@ -40199,7 +40199,7 @@
         <v>921</v>
       </c>
       <c r="C484" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D484" s="1">
         <v>2006</v>
@@ -40264,7 +40264,7 @@
         <v>922</v>
       </c>
       <c r="C485" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D485" s="1">
         <v>2018</v>
@@ -40325,7 +40325,7 @@
         <v>923</v>
       </c>
       <c r="C486" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D486" s="1">
         <v>2006</v>
@@ -40390,7 +40390,7 @@
         <v>924</v>
       </c>
       <c r="C487" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D487" s="1">
         <v>2018</v>
@@ -40451,7 +40451,7 @@
         <v>925</v>
       </c>
       <c r="C488" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D488" s="1">
         <v>2018</v>
@@ -40516,7 +40516,7 @@
         <v>925</v>
       </c>
       <c r="C489" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D489" s="1">
         <v>2021</v>
@@ -40577,7 +40577,7 @@
         <v>926</v>
       </c>
       <c r="C490" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D490" s="1">
         <v>2006</v>
@@ -40642,7 +40642,7 @@
         <v>927</v>
       </c>
       <c r="C491" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D491" s="1">
         <v>2017</v>
@@ -40703,7 +40703,7 @@
         <v>928</v>
       </c>
       <c r="C492" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D492" s="1">
         <v>2018</v>
@@ -40768,7 +40768,7 @@
         <v>928</v>
       </c>
       <c r="C493" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D493" s="1">
         <v>2021</v>
@@ -40829,7 +40829,7 @@
         <v>929</v>
       </c>
       <c r="C494" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D494" s="1">
         <v>2018</v>
@@ -40890,7 +40890,7 @@
         <v>930</v>
       </c>
       <c r="C495" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D495" s="1">
         <v>2018</v>
@@ -40951,7 +40951,7 @@
         <v>931</v>
       </c>
       <c r="C496" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D496" s="1">
         <v>2006</v>
@@ -41016,7 +41016,7 @@
         <v>932</v>
       </c>
       <c r="C497" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D497" s="1">
         <v>2004</v>
@@ -41079,7 +41079,7 @@
         <v>933</v>
       </c>
       <c r="C498" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D498" s="1">
         <v>2018</v>
@@ -41140,7 +41140,7 @@
         <v>934</v>
       </c>
       <c r="C499" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D499" s="1">
         <v>2018</v>
@@ -41205,7 +41205,7 @@
         <v>934</v>
       </c>
       <c r="C500" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D500" s="1">
         <v>2021</v>
@@ -41331,7 +41331,7 @@
         <v>936</v>
       </c>
       <c r="C502" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D502" s="1">
         <v>2018</v>
@@ -41392,7 +41392,7 @@
         <v>937</v>
       </c>
       <c r="C503" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D503" s="1">
         <v>2018</v>
@@ -41457,7 +41457,7 @@
         <v>937</v>
       </c>
       <c r="C504" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D504" s="1">
         <v>2021</v>
@@ -41518,7 +41518,7 @@
         <v>938</v>
       </c>
       <c r="C505" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D505" s="1">
         <v>2018</v>
@@ -41579,7 +41579,7 @@
         <v>939</v>
       </c>
       <c r="C506" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D506" s="1">
         <v>2006</v>
@@ -41644,7 +41644,7 @@
         <v>940</v>
       </c>
       <c r="C507" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D507" s="1">
         <v>2018</v>
@@ -41705,7 +41705,7 @@
         <v>941</v>
       </c>
       <c r="C508" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D508" s="1">
         <v>2018</v>
@@ -41766,7 +41766,7 @@
         <v>942</v>
       </c>
       <c r="C509" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D509" s="1">
         <v>2006</v>
@@ -41896,7 +41896,7 @@
         <v>944</v>
       </c>
       <c r="C511" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D511" s="1">
         <v>2018</v>
@@ -41957,7 +41957,7 @@
         <v>945</v>
       </c>
       <c r="C512" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D512" s="1">
         <v>2006</v>
@@ -42022,7 +42022,7 @@
         <v>946</v>
       </c>
       <c r="C513" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D513" s="1">
         <v>2006</v>
@@ -42087,7 +42087,7 @@
         <v>947</v>
       </c>
       <c r="C514" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D514" s="1">
         <v>2018</v>
@@ -42152,7 +42152,7 @@
         <v>947</v>
       </c>
       <c r="C515" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D515" s="1">
         <v>2021</v>
@@ -42213,7 +42213,7 @@
         <v>948</v>
       </c>
       <c r="C516" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D516" s="1">
         <v>2017</v>
@@ -42274,7 +42274,7 @@
         <v>949</v>
       </c>
       <c r="C517" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D517" s="1">
         <v>2018</v>
@@ -42335,7 +42335,7 @@
         <v>950</v>
       </c>
       <c r="C518" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D518" s="1">
         <v>2018</v>
@@ -42400,7 +42400,7 @@
         <v>950</v>
       </c>
       <c r="C519" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D519" s="1">
         <v>2021</v>
@@ -42461,7 +42461,7 @@
         <v>951</v>
       </c>
       <c r="C520" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D520" s="1">
         <v>2008</v>
@@ -42526,7 +42526,7 @@
         <v>952</v>
       </c>
       <c r="C521" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D521" s="1">
         <v>2018</v>
@@ -42587,7 +42587,7 @@
         <v>953</v>
       </c>
       <c r="C522" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D522" s="1">
         <v>2006</v>
@@ -42652,7 +42652,7 @@
         <v>954</v>
       </c>
       <c r="C523" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D523" s="1">
         <v>2006</v>
@@ -42780,7 +42780,7 @@
         <v>956</v>
       </c>
       <c r="C525" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D525" s="1">
         <v>2006</v>
@@ -42967,7 +42967,7 @@
         <v>959</v>
       </c>
       <c r="C528" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D528" s="1">
         <v>2018</v>
@@ -43156,7 +43156,7 @@
         <v>961</v>
       </c>
       <c r="C531" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D531" s="1">
         <v>2017</v>
@@ -43280,7 +43280,7 @@
         <v>963</v>
       </c>
       <c r="C533" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D533" s="1">
         <v>2004</v>
@@ -43467,7 +43467,7 @@
         <v>966</v>
       </c>
       <c r="C536" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D536" s="1">
         <v>2006</v>
@@ -43532,7 +43532,7 @@
         <v>967</v>
       </c>
       <c r="C537" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D537" s="1">
         <v>2006</v>
@@ -43717,7 +43717,7 @@
         <v>970</v>
       </c>
       <c r="C540" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D540" s="1">
         <v>2006</v>
@@ -43782,7 +43782,7 @@
         <v>971</v>
       </c>
       <c r="C541" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D541" s="1">
         <v>2006</v>
@@ -44032,7 +44032,7 @@
         <v>974</v>
       </c>
       <c r="C545" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D545" s="1">
         <v>2018</v>
@@ -44152,7 +44152,7 @@
         <v>976</v>
       </c>
       <c r="C547" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D547" s="1">
         <v>2018</v>
@@ -44402,7 +44402,7 @@
         <v>978</v>
       </c>
       <c r="C551" t="s">
-        <v>1148</v>
+        <v>1111</v>
       </c>
       <c r="D551" s="1">
         <v>2015</v>
@@ -44467,7 +44467,7 @@
         <v>978</v>
       </c>
       <c r="C552" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D552" s="1">
         <v>2018</v>
@@ -44532,7 +44532,7 @@
         <v>978</v>
       </c>
       <c r="C553" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D553" s="1">
         <v>2021</v>
@@ -44658,7 +44658,7 @@
         <v>979</v>
       </c>
       <c r="C555" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D555" s="1">
         <v>2017</v>
@@ -44969,7 +44969,7 @@
         <v>983</v>
       </c>
       <c r="C560" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D560" s="1">
         <v>2006</v>
@@ -45221,7 +45221,7 @@
         <v>986</v>
       </c>
       <c r="C564" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D564" s="1">
         <v>2018</v>
@@ -45282,7 +45282,7 @@
         <v>987</v>
       </c>
       <c r="C565" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D565" s="1">
         <v>2018</v>
@@ -45465,7 +45465,7 @@
         <v>990</v>
       </c>
       <c r="C568" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D568" s="1">
         <v>2018</v>
@@ -45530,7 +45530,7 @@
         <v>990</v>
       </c>
       <c r="C569" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D569" s="1">
         <v>2021</v>
@@ -45591,7 +45591,7 @@
         <v>991</v>
       </c>
       <c r="C570" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D570" s="1">
         <v>2006</v>
@@ -45721,7 +45721,7 @@
         <v>993</v>
       </c>
       <c r="C572" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D572" s="1">
         <v>2006</v>
@@ -45786,7 +45786,7 @@
         <v>994</v>
       </c>
       <c r="C573" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D573" s="1">
         <v>2018</v>
@@ -45910,7 +45910,7 @@
         <v>996</v>
       </c>
       <c r="C575" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D575" s="1">
         <v>2018</v>
@@ -45971,7 +45971,7 @@
         <v>997</v>
       </c>
       <c r="C576" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D576" s="1">
         <v>2004</v>
@@ -46036,7 +46036,7 @@
         <v>998</v>
       </c>
       <c r="C577" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D577" s="1">
         <v>2004</v>
@@ -46101,7 +46101,7 @@
         <v>998</v>
       </c>
       <c r="C578" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D578" s="1">
         <v>2017</v>
@@ -46166,7 +46166,7 @@
         <v>999</v>
       </c>
       <c r="C579" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D579" s="1">
         <v>2006</v>
@@ -46231,7 +46231,7 @@
         <v>1000</v>
       </c>
       <c r="C580" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D580" s="1">
         <v>2018</v>
@@ -46351,7 +46351,7 @@
         <v>1002</v>
       </c>
       <c r="C582" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D582" s="1">
         <v>2018</v>
@@ -46412,7 +46412,7 @@
         <v>1003</v>
       </c>
       <c r="C583" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D583" s="1">
         <v>2018</v>
@@ -46473,7 +46473,7 @@
         <v>1004</v>
       </c>
       <c r="C584" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D584" s="1">
         <v>2006</v>
@@ -46538,7 +46538,7 @@
         <v>1005</v>
       </c>
       <c r="C585" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D585" s="1">
         <v>2004</v>
@@ -46601,7 +46601,7 @@
         <v>1006</v>
       </c>
       <c r="C586" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D586" s="1">
         <v>2006</v>
@@ -46729,7 +46729,7 @@
         <v>1007</v>
       </c>
       <c r="C588" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D588" s="1">
         <v>2006</v>
@@ -46794,7 +46794,7 @@
         <v>1008</v>
       </c>
       <c r="C589" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D589" s="1">
         <v>2006</v>
@@ -46859,7 +46859,7 @@
         <v>1009</v>
       </c>
       <c r="C590" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D590" s="1">
         <v>2006</v>
@@ -46924,7 +46924,7 @@
         <v>1010</v>
       </c>
       <c r="C591" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D591" s="1">
         <v>2006</v>
@@ -46989,7 +46989,7 @@
         <v>1011</v>
       </c>
       <c r="C592" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D592" s="1">
         <v>2006</v>
@@ -47054,7 +47054,7 @@
         <v>1012</v>
       </c>
       <c r="C593" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D593" s="1">
         <v>2017</v>
@@ -47178,7 +47178,7 @@
         <v>1013</v>
       </c>
       <c r="C595" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D595" s="1">
         <v>2004</v>
@@ -47306,7 +47306,7 @@
         <v>1013</v>
       </c>
       <c r="C597" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D597" s="1">
         <v>2017</v>
@@ -47371,7 +47371,7 @@
         <v>1014</v>
       </c>
       <c r="C598" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D598" s="1">
         <v>2006</v>
@@ -47436,7 +47436,7 @@
         <v>1015</v>
       </c>
       <c r="C599" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D599" s="1">
         <v>2006</v>
@@ -47501,7 +47501,7 @@
         <v>1016</v>
       </c>
       <c r="C600" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D600" s="1">
         <v>2006</v>
@@ -47566,7 +47566,7 @@
         <v>1017</v>
       </c>
       <c r="C601" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D601" s="1">
         <v>2006</v>
@@ -47631,7 +47631,7 @@
         <v>1018</v>
       </c>
       <c r="C602" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D602" s="1">
         <v>2006</v>
@@ -47757,7 +47757,7 @@
         <v>1020</v>
       </c>
       <c r="C604" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D604" s="1">
         <v>2004</v>
@@ -47822,7 +47822,7 @@
         <v>1020</v>
       </c>
       <c r="C605" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D605" s="1">
         <v>2017</v>
@@ -47887,7 +47887,7 @@
         <v>1021</v>
       </c>
       <c r="C606" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D606" s="1">
         <v>2018</v>
@@ -47948,7 +47948,7 @@
         <v>1022</v>
       </c>
       <c r="C607" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D607" s="1">
         <v>2006</v>
@@ -48013,7 +48013,7 @@
         <v>1023</v>
       </c>
       <c r="C608" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D608" s="1">
         <v>2006</v>
@@ -48141,7 +48141,7 @@
         <v>1025</v>
       </c>
       <c r="C610" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D610" s="1">
         <v>2006</v>
@@ -48265,7 +48265,7 @@
         <v>1027</v>
       </c>
       <c r="C612" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D612" s="1">
         <v>2018</v>
@@ -48330,7 +48330,7 @@
         <v>1027</v>
       </c>
       <c r="C613" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D613" s="1">
         <v>2021</v>
@@ -48519,7 +48519,7 @@
         <v>1030</v>
       </c>
       <c r="C616" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D616" s="1">
         <v>2006</v>
@@ -48584,7 +48584,7 @@
         <v>1031</v>
       </c>
       <c r="C617" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D617" s="1">
         <v>2006</v>
@@ -48649,7 +48649,7 @@
         <v>1032</v>
       </c>
       <c r="C618" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D618" s="1">
         <v>2006</v>
@@ -48714,7 +48714,7 @@
         <v>1033</v>
       </c>
       <c r="C619" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D619" s="1">
         <v>2006</v>
@@ -48779,7 +48779,7 @@
         <v>1034</v>
       </c>
       <c r="C620" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D620" s="1">
         <v>2006</v>
@@ -48844,7 +48844,7 @@
         <v>1035</v>
       </c>
       <c r="C621" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D621" s="1">
         <v>2006</v>
@@ -49031,7 +49031,7 @@
         <v>1038</v>
       </c>
       <c r="C624" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D624" s="1">
         <v>2018</v>
@@ -49096,7 +49096,7 @@
         <v>1038</v>
       </c>
       <c r="C625" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D625" s="1">
         <v>2021</v>
@@ -49726,7 +49726,7 @@
         <v>1047</v>
       </c>
       <c r="C635" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D635" s="1">
         <v>2004</v>
@@ -49791,7 +49791,7 @@
         <v>1047</v>
       </c>
       <c r="C636" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D636" s="1">
         <v>2017</v>
@@ -49856,7 +49856,7 @@
         <v>1048</v>
       </c>
       <c r="C637" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D637" s="1">
         <v>2006</v>
@@ -49921,7 +49921,7 @@
         <v>1049</v>
       </c>
       <c r="C638" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D638" s="1">
         <v>2004</v>
@@ -49986,7 +49986,7 @@
         <v>1050</v>
       </c>
       <c r="C639" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D639" s="1">
         <v>2018</v>
@@ -50051,7 +50051,7 @@
         <v>1050</v>
       </c>
       <c r="C640" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D640" s="1">
         <v>2021</v>
@@ -50112,7 +50112,7 @@
         <v>1051</v>
       </c>
       <c r="C641" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D641" s="1">
         <v>2006</v>
@@ -50177,7 +50177,7 @@
         <v>1052</v>
       </c>
       <c r="C642" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D642" s="1">
         <v>2017</v>
@@ -50238,7 +50238,7 @@
         <v>1053</v>
       </c>
       <c r="C643" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D643" s="1">
         <v>2006</v>
@@ -50303,7 +50303,7 @@
         <v>1054</v>
       </c>
       <c r="C644" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D644" s="1">
         <v>2018</v>
@@ -50368,7 +50368,7 @@
         <v>1054</v>
       </c>
       <c r="C645" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D645" s="1">
         <v>2021</v>
@@ -50429,7 +50429,7 @@
         <v>1055</v>
       </c>
       <c r="C646" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D646" s="1">
         <v>2004</v>
@@ -50494,7 +50494,7 @@
         <v>1055</v>
       </c>
       <c r="C647" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D647" s="1">
         <v>2017</v>
@@ -50559,7 +50559,7 @@
         <v>1056</v>
       </c>
       <c r="C648" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D648" s="1">
         <v>2006</v>
@@ -50624,7 +50624,7 @@
         <v>1057</v>
       </c>
       <c r="C649" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D649" s="1">
         <v>2006</v>
@@ -50689,7 +50689,7 @@
         <v>1058</v>
       </c>
       <c r="C650" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D650" s="1">
         <v>2004</v>
@@ -50754,7 +50754,7 @@
         <v>1058</v>
       </c>
       <c r="C651" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D651" s="1">
         <v>2017</v>
@@ -50819,7 +50819,7 @@
         <v>1059</v>
       </c>
       <c r="C652" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D652" s="1">
         <v>2006</v>
@@ -50947,7 +50947,7 @@
         <v>1061</v>
       </c>
       <c r="C654" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D654" s="1">
         <v>2006</v>
@@ -51012,7 +51012,7 @@
         <v>1062</v>
       </c>
       <c r="C655" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D655" s="1">
         <v>2018</v>
@@ -51077,7 +51077,7 @@
         <v>1062</v>
       </c>
       <c r="C656" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D656" s="1">
         <v>2021</v>
@@ -51138,7 +51138,7 @@
         <v>1063</v>
       </c>
       <c r="C657" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D657" s="1">
         <v>2006</v>
@@ -51203,7 +51203,7 @@
         <v>1064</v>
       </c>
       <c r="C658" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D658" s="1">
         <v>2018</v>
@@ -51268,7 +51268,7 @@
         <v>1064</v>
       </c>
       <c r="C659" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D659" s="1">
         <v>2021</v>
@@ -51329,7 +51329,7 @@
         <v>1065</v>
       </c>
       <c r="C660" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D660" s="1">
         <v>2018</v>
@@ -51390,7 +51390,7 @@
         <v>1066</v>
       </c>
       <c r="C661" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D661" s="1">
         <v>2006</v>
@@ -51455,7 +51455,7 @@
         <v>1067</v>
       </c>
       <c r="C662" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D662" s="1">
         <v>2018</v>
@@ -51520,7 +51520,7 @@
         <v>1067</v>
       </c>
       <c r="C663" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D663" s="1">
         <v>2021</v>
@@ -51581,7 +51581,7 @@
         <v>1068</v>
       </c>
       <c r="C664" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D664" s="1">
         <v>2018</v>
@@ -51646,7 +51646,7 @@
         <v>1068</v>
       </c>
       <c r="C665" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D665" s="1">
         <v>2021</v>
@@ -51709,7 +51709,7 @@
         <v>1069</v>
       </c>
       <c r="C666" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D666" s="1">
         <v>2018</v>
@@ -51770,7 +51770,7 @@
         <v>1070</v>
       </c>
       <c r="C667" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D667" s="1">
         <v>2018</v>
@@ -51831,7 +51831,7 @@
         <v>1071</v>
       </c>
       <c r="C668" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D668" s="1">
         <v>2006</v>
@@ -51896,7 +51896,7 @@
         <v>1072</v>
       </c>
       <c r="C669" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D669" s="1">
         <v>2006</v>
@@ -51961,7 +51961,7 @@
         <v>1073</v>
       </c>
       <c r="C670" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D670" s="1">
         <v>2018</v>
@@ -52026,7 +52026,7 @@
         <v>1073</v>
       </c>
       <c r="C671" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D671" s="1">
         <v>2021</v>
@@ -52087,7 +52087,7 @@
         <v>1074</v>
       </c>
       <c r="C672" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D672" s="1">
         <v>2006</v>
@@ -52152,7 +52152,7 @@
         <v>1075</v>
       </c>
       <c r="C673" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D673" s="1">
         <v>2006</v>
@@ -52217,7 +52217,7 @@
         <v>1076</v>
       </c>
       <c r="C674" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D674" s="1">
         <v>2006</v>
@@ -52282,7 +52282,7 @@
         <v>1077</v>
       </c>
       <c r="C675" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D675" s="1">
         <v>2006</v>
@@ -52412,7 +52412,7 @@
         <v>1078</v>
       </c>
       <c r="C677" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D677" s="1">
         <v>2021</v>
@@ -52601,7 +52601,7 @@
         <v>1079</v>
       </c>
       <c r="C680" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D680" s="1">
         <v>2018</v>
@@ -52666,7 +52666,7 @@
         <v>1080</v>
       </c>
       <c r="C681" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D681" s="1">
         <v>2018</v>
@@ -52790,7 +52790,7 @@
         <v>1082</v>
       </c>
       <c r="C683" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D683" s="1">
         <v>2018</v>
@@ -52855,7 +52855,7 @@
         <v>1082</v>
       </c>
       <c r="C684" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D684" s="1">
         <v>2021</v>
@@ -52916,7 +52916,7 @@
         <v>1083</v>
       </c>
       <c r="C685" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D685" s="1">
         <v>2018</v>
@@ -52981,7 +52981,7 @@
         <v>1083</v>
       </c>
       <c r="C686" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D686" s="1">
         <v>2021</v>
@@ -53042,7 +53042,7 @@
         <v>1084</v>
       </c>
       <c r="C687" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D687" s="1">
         <v>2018</v>
@@ -53103,7 +53103,7 @@
         <v>1085</v>
       </c>
       <c r="C688" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D688" s="1">
         <v>2018</v>
@@ -53164,7 +53164,7 @@
         <v>1086</v>
       </c>
       <c r="C689" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D689" s="1">
         <v>2018</v>
@@ -53229,7 +53229,7 @@
         <v>1086</v>
       </c>
       <c r="C690" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D690" s="1">
         <v>2021</v>
@@ -53353,7 +53353,7 @@
         <v>1088</v>
       </c>
       <c r="C692" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D692" s="1">
         <v>2018</v>
@@ -53418,7 +53418,7 @@
         <v>1088</v>
       </c>
       <c r="C693" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D693" s="1">
         <v>2021</v>
@@ -53479,7 +53479,7 @@
         <v>1089</v>
       </c>
       <c r="C694" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D694" s="1">
         <v>2017</v>
@@ -53717,7 +53717,7 @@
         <v>1092</v>
       </c>
       <c r="C698" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D698" s="1">
         <v>2018</v>
@@ -54091,7 +54091,7 @@
         <v>1098</v>
       </c>
       <c r="C704" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D704" s="1">
         <v>2015</v>
@@ -54150,7 +54150,7 @@
         <v>1098</v>
       </c>
       <c r="C705" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D705" s="1">
         <v>2015</v>
@@ -54390,7 +54390,7 @@
         <v>1102</v>
       </c>
       <c r="C709" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D709" s="1">
         <v>2017</v>
@@ -54577,7 +54577,7 @@
         <v>1105</v>
       </c>
       <c r="C712" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D712" s="1">
         <v>2006</v>
@@ -54642,7 +54642,7 @@
         <v>1106</v>
       </c>
       <c r="C713" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D713" s="1">
         <v>2004</v>
@@ -54705,7 +54705,7 @@
         <v>1107</v>
       </c>
       <c r="C714" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D714" s="1">
         <v>2006</v>
@@ -54770,7 +54770,7 @@
         <v>1107</v>
       </c>
       <c r="C715" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D715" s="1">
         <v>2006</v>
@@ -54835,7 +54835,7 @@
         <v>1108</v>
       </c>
       <c r="C716" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D716" s="1">
         <v>2017</v>
